--- a/data/trending_integrated_20260910_09.xlsx
+++ b/data/trending_integrated_20260910_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8400</v>
+        <v>8810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+47.11%</t>
+          <t>+18.73%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>385</v>
+        <v>504</v>
       </c>
       <c r="H2" t="n">
         <v>1.17</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5710</v>
+        <v>7420</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N2" t="n">
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>4849000000</v>
+        <v>25413713280</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>세계 폐암학회 발표 및 항암제 내성 극복 연구 결과 기반 기대감. 오가노이드 실험 성공 및 임상 2상 전초전 연구 언급.</t>
+          <t>항암제 내성 극복 및 오가노이드 실험 성공 관련 긍정적 뉴스. FDA 임상 2상 성공 기대감으로 급등세. 4연상 이상 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['폐암학회', '항암제 내성', '오가노이드']</t>
+          <t>['항암제', '오가노이드', 'FDA']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,60 +655,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>159800</v>
+        <v>13910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.80%</t>
+          <t>+15.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>322</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
-        <v>15.65</v>
+        <v>0.03</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>138000</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13910</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>12720</v>
       </c>
       <c r="N3" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>20781000000</v>
+        <v>39697337350</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>36200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8920</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제마진 고공행진에 따른 긍정적 전망. JP모건 대량매수 패턴 언급.</t>
+          <t>이란 사태 고조로 인한 국제 유가 급등 및 흥구석유 주가 상승 기대감. 일시적인 유가 변동성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가 폭등', '정제마진', 'JP모건']</t>
+          <t>['국제유가', '이란', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,67 +740,67 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14770</v>
+        <v>157700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+7.81%</t>
+          <t>+2.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.34</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="H4" t="n">
-        <v>2.89</v>
+        <v>15.65</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13700</v>
+        <v>153500</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>155500</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>160800</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>154500</v>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>15.25</v>
       </c>
       <c r="O4" t="n">
-        <v>6035000000</v>
+        <v>57532692700</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>160800</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>87700</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 강세 및 AI 관련주로의 편입 기대감. 거래량 증가 및 상환가 가능성 언급.</t>
+          <t>유가 폭등 및 정제 마진 호조에 따른 긍정적 전망. JP모건 대량 매수 패턴 언급. 단기적 시세 영향.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '거래량']</t>
+          <t>['유가', '정제마진', 'JP모건']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1876000</v>
+        <v>1864000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+4.63%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F5" t="n">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G5" t="n">
-        <v>2653</v>
+        <v>2168</v>
       </c>
       <c r="H5" t="n">
         <v>50.67</v>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1793000</v>
+        <v>1856000</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1879000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1890000</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1858000</v>
       </c>
       <c r="N5" t="n">
         <v>50.66</v>
       </c>
       <c r="O5" t="n">
-        <v>170352000000</v>
+        <v>579305119500</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>293000</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 신고가 돌파 및 가치 재평가 시작 전망. 연말 300만 돌파 및 250만 목표 제시.</t>
+          <t>SK하이닉스 ADR 및 미국 반도체 관련주 동반 상승에 따른 기대감. AI 관련 긍정적 전망과 자사주 매수 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['ADR', '가치 재평가', '신고가']</t>
+          <t>['ADR', '반도체', 'AI']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89600</v>
+        <v>268000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>795</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>471</v>
       </c>
       <c r="G6" t="n">
-        <v>507</v>
+        <v>2535</v>
       </c>
       <c r="H6" t="n">
-        <v>23.65</v>
+        <v>46.81</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>89500</v>
+        <v>269500</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>269000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>270500</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>267500</v>
       </c>
       <c r="N6" t="n">
-        <v>23.61</v>
+        <v>46.85</v>
       </c>
       <c r="O6" t="n">
-        <v>6725000000</v>
+        <v>281135630000</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>71600</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 관련 사업 호재 및 미국 원전 건설 수주 기대감. 웨스턴하우스 지분 인수 가능성 언급.</t>
+          <t>이재용·홍라희 지분 관련 언급 및 하이닉스 ADR 상승에 따른 기대감. 실질적인 주가 상승 근거는 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', '미국 건설']</t>
+          <t>['지분', '기대감', 'ADR']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>269000</v>
+        <v>89100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>770</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>2699</v>
+        <v>512</v>
       </c>
       <c r="H7" t="n">
-        <v>46.81</v>
+        <v>23.65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>269500</v>
+        <v>91700</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>90700</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.85</v>
+        <v>23.61</v>
       </c>
       <c r="O7" t="n">
-        <v>104779000000</v>
+        <v>23696976450</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1086,20 +1086,20 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>홍라희 여사 물량 소화 및 이재용 지분 취득 관련 언급. 하이닉스 ADR 급등에 따른 기대감 형성.</t>
+          <t>미국 원전 건설 수주 확정 및 웨스턴하우스 지분 인수 관련 호재. '팀코리아' 관련 긍정적 전망 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['홍라희', '이재용', '하이닉스 ADR']</t>
+          <t>['원전', '수주', '웨스턴하우스']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,191 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18770</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-3.50%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G8" t="n">
+        <v>136</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>19450</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18900</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19190</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18670</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15402967435</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>원전 관련 건설 수주 기대감과 함께 주가 급락 우려 및 매도 의견 대립. 부정적 전망 다수.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['원전', '건설주', '급락']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14370</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-3.94%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>259</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>14960</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15040</v>
+      </c>
+      <c r="L9" t="n">
+        <v>15040</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14320</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26089608820</v>
+      </c>
+      <c r="P9" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1263</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>미국 광통신 및 AI 관련주 강세에 따른 대한광통신 주가 상승 기대감. 거래량 증가 및 120일선 돌파 가능성.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '거래량']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>010170</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_09.xlsx
+++ b/data/trending_integrated_20260910_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8810</v>
+        <v>5030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.73%</t>
+          <t>+151.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>504</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
-        <v>1.17</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7420</v>
+        <v>2000</v>
       </c>
       <c r="K2" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="L2" t="n">
-        <v>9100</v>
+        <v>5660</v>
       </c>
       <c r="M2" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="N2" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>25413713280</v>
+        <v>284467308563</v>
       </c>
       <c r="P2" t="n">
-        <v>21500</v>
+        <v>5660</v>
       </c>
       <c r="Q2" t="n">
-        <v>2300</v>
+        <v>4000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>항암제 내성 극복 및 오가노이드 실험 성공 관련 긍정적 뉴스. FDA 임상 2상 성공 기대감으로 급등세. 4연상 이상 목표.</t>
+          <t>스팩주 특성상 단기 수익 기대. 신재생 에너지 합병 관련 언급 있으며, 2천원 종가 예상 및 타이밍 중요성 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['항암제', '오가노이드', 'FDA']</t>
+          <t>['스팩주', '신재생 에너지', '단기 수익']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>0197V0</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13910</v>
+        <v>14910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.05%</t>
+          <t>+23.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -693,7 +693,7 @@
         <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>13910</v>
+        <v>14910</v>
       </c>
       <c r="M3" t="n">
         <v>12720</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>39697337350</v>
+        <v>106797590820</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -711,14 +711,14 @@
         <v>8920</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>245000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이란 사태 고조로 인한 국제 유가 급등 및 흥구석유 주가 상승 기대감. 일시적인 유가 변동성 언급.</t>
+          <t>중동 긴장 고조 및 유가 급등에 따른 주가 상승 기대. 트럼프 발언 및 유가 전망 관련 분석.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '급등']</t>
+          <t>['유가 급등', '중동 긴장', '트럼프']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157700</v>
+        <v>8470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+2.74%</t>
+          <t>+14.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>334</v>
+        <v>626</v>
       </c>
       <c r="H4" t="n">
-        <v>15.65</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>153500</v>
+        <v>7420</v>
       </c>
       <c r="K4" t="n">
-        <v>155500</v>
+        <v>8000</v>
       </c>
       <c r="L4" t="n">
-        <v>160800</v>
+        <v>9100</v>
       </c>
       <c r="M4" t="n">
-        <v>154500</v>
+        <v>8000</v>
       </c>
       <c r="N4" t="n">
-        <v>15.25</v>
+        <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>57532692700</v>
+        <v>38687484830</v>
       </c>
       <c r="P4" t="n">
-        <v>160800</v>
+        <v>21500</v>
       </c>
       <c r="Q4" t="n">
-        <v>87700</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제 마진 호조에 따른 긍정적 전망. JP모건 대량 매수 패턴 언급. 단기적 시세 영향.</t>
+          <t>세계 폐암학회 참여 및 키투르다 관련 임상 결과 발표. 항암제 내성 극복 기대감으로 인한 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', 'JP모건']</t>
+          <t>['폐암학회', '키투르다', '항암제 내성']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1864000</v>
+        <v>161700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+5.34%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>794</v>
+        <v>186</v>
       </c>
       <c r="F5" t="n">
-        <v>469</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>2168</v>
+        <v>475</v>
       </c>
       <c r="H5" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K5" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L5" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M5" t="n">
-        <v>1858000</v>
+        <v>154500</v>
       </c>
       <c r="N5" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O5" t="n">
-        <v>579305119500</v>
+        <v>149308564200</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q5" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 및 미국 반도체 관련주 동반 상승에 따른 기대감. AI 관련 긍정적 전망과 자사주 매수 가능성 언급.</t>
+          <t>유가 폭등 및 정제마진 개선에 따른 긍정적 전망. 외인 대량 매수 이후 패턴 분석 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['ADR', '반도체', 'AI']</t>
+          <t>['유가', '정제마진', '외인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268000</v>
+        <v>2125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>795</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>471</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>2535</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>46.81</v>
+        <v>0.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>269500</v>
+        <v>2085</v>
       </c>
       <c r="K6" t="n">
-        <v>269000</v>
+        <v>2255</v>
       </c>
       <c r="L6" t="n">
-        <v>270500</v>
+        <v>2395</v>
       </c>
       <c r="M6" t="n">
-        <v>267500</v>
+        <v>2085</v>
       </c>
       <c r="N6" t="n">
-        <v>46.85</v>
+        <v>0.51</v>
       </c>
       <c r="O6" t="n">
-        <v>281135630000</v>
+        <v>12340697343</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2930</v>
       </c>
       <c r="Q6" t="n">
-        <v>71600</v>
+        <v>910</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이재용·홍라희 지분 관련 언급 및 하이닉스 ADR 상승에 따른 기대감. 실질적인 주가 상승 근거는 부족.</t>
+          <t>거래량 증가 및 주가 상승에 대한 기대감. 경영진 긍정 평가 및 매물 소화 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['지분', '기대감', 'ADR']</t>
+          <t>['거래량', '주가 상승', '경영진']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89100</v>
+        <v>1849000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>794</v>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>468</v>
       </c>
       <c r="G7" t="n">
-        <v>512</v>
+        <v>1657</v>
       </c>
       <c r="H7" t="n">
-        <v>23.65</v>
+        <v>50.67</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>91700</v>
+        <v>1856000</v>
       </c>
       <c r="K7" t="n">
-        <v>90000</v>
+        <v>1879000</v>
       </c>
       <c r="L7" t="n">
-        <v>90700</v>
+        <v>1890000</v>
       </c>
       <c r="M7" t="n">
-        <v>89000</v>
+        <v>1848000</v>
       </c>
       <c r="N7" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="O7" t="n">
-        <v>23696976450</v>
+        <v>1075477771000</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>293000</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전 건설 수주 확정 및 웨스턴하우스 지분 인수 관련 호재. '팀코리아' 관련 긍정적 전망 및 주가 상승 기대.</t>
+          <t>ADR 상승에 따른 본장 급등 기대감. 매물 부족 및 저점 매수 찬스 언급. 200 돌파 가능성 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '수주', '웨스턴하우스']</t>
+          <t>['ADR', '급등 기대', '저점 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18770</v>
+        <v>267000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>792</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>464</v>
       </c>
       <c r="G8" t="n">
-        <v>136</v>
+        <v>2052</v>
       </c>
       <c r="H8" t="n">
-        <v>10.64</v>
+        <v>46.81</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>19450</v>
+        <v>269500</v>
       </c>
       <c r="K8" t="n">
-        <v>18900</v>
+        <v>269000</v>
       </c>
       <c r="L8" t="n">
-        <v>19190</v>
+        <v>270500</v>
       </c>
       <c r="M8" t="n">
-        <v>18670</v>
+        <v>266500</v>
       </c>
       <c r="N8" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="O8" t="n">
-        <v>15402967435</v>
+        <v>532159491250</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>71600</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 관련 건설 수주 기대감과 함께 주가 급락 우려 및 매도 의견 대립. 부정적 전망 다수.</t>
+          <t>하이닉스 대비 삼성전자 주가 부진에 대한 언급 다수. 일부 투자자는 외국인 매도세 및 자사주 매입 관련 리스크 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '건설주', '급락']</t>
+          <t>['하이닉스', '외국인 매도', '자사주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,99 +1200,559 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14370</v>
+        <v>19020</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.34</v>
+        <v>-0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>259</v>
+        <v>166</v>
       </c>
       <c r="H9" t="n">
-        <v>2.89</v>
+        <v>10.64</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14960</v>
+        <v>19450</v>
       </c>
       <c r="K9" t="n">
-        <v>15040</v>
+        <v>18900</v>
       </c>
       <c r="L9" t="n">
-        <v>15040</v>
+        <v>19220</v>
       </c>
       <c r="M9" t="n">
-        <v>14320</v>
+        <v>18670</v>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>10.85</v>
       </c>
       <c r="O9" t="n">
-        <v>26089608820</v>
+        <v>29561633500</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1263</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신 및 AI 관련주 강세에 따른 대한광통신 주가 상승 기대감. 거래량 증가 및 120일선 돌파 가능성.</t>
+          <t>원전 관련 기대감 및 중동 정세 언급. 일부 투자자는 주가 하락 이유 분석 및 반등 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '거래량']</t>
+          <t>['원전', '중동', '주가 분석']</t>
         </is>
       </c>
       <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>89500</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-2.40%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E10" t="n">
+        <v>117</v>
+      </c>
+      <c r="F10" t="n">
+        <v>83</v>
+      </c>
+      <c r="G10" t="n">
+        <v>606</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>91700</v>
+      </c>
+      <c r="K10" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>90700</v>
+      </c>
+      <c r="M10" t="n">
+        <v>88400</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="O10" t="n">
+        <v>47170860100</v>
+      </c>
+      <c r="P10" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>원전 관련주로서 최고 호재가 부각되며 10만원 터치 기대감이 형성됨. 웨스팅하우스 지분 인수 가능성 및 '팀 코리아'의 미국 원전 건설 참여 소식이 긍정적 요인으로 작용하나, 외인 트릭 및 공매도에 대한 경계심도 존재함.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['원전', '웨스팅하우스', '팀 코리아']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>12</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>14520</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-2.94%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E11" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>291</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>14960</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15040</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15040</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14190</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O11" t="n">
+        <v>45206750260</v>
+      </c>
+      <c r="P11" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1263</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-191000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>미국 광통신 관련주로 부각되며 16000원 돌파 기대감이 형성되었으나, 외인 인기 순위 1위 등에도 불구하고 상승 추세는 불확실함. 시외 상승 후 급락 가능성도 제기됨.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI 관련주', '시간외']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13740</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-4.05%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G12" t="n">
+        <v>183</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>14320</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13800</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="O12" t="n">
+        <v>45246109425</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30200</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3540</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-82000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>공매도 금지 지정 관련 언급. 일부 투자자는 주가 하락 예상 및 단타 매매 전략 제시. 그래핀 개발 관련 내용도 포함.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['공매도 금지', '주가 하락', '그래핀']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>032820</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6510</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-5.10%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42</v>
+      </c>
+      <c r="F13" t="n">
+        <v>32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>98</v>
+      </c>
+      <c r="H13" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6860</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6820</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6490</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4586562845</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6030</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>외국인 매도세 및 주가 하락에 대한 우려. 로봇 및 반도체 관련 기대감에도 불구하고 주가 흐름 부진.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['외국인 매도', '로봇', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0220W0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12350</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-5.22%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E14" t="n">
+        <v>43</v>
+      </c>
+      <c r="F14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>38</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>13030</v>
+      </c>
+      <c r="K14" t="n">
+        <v>13160</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13240</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12150</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O14" t="n">
+        <v>35283481460</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3500억 달러 규모의 대미 투자 관련 호재가 언급되었으나, 주가는 5% 이상 하락하며 투자자들의 불안감이 커지고 있음. 일부 투자자는 매도 후 다른 종목으로 이동함.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['대미 투자', '원전', '악재']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>012210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_09.xlsx
+++ b/data/trending_integrated_20260910_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5030</v>
+        <v>4800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+151.50%</t>
+          <t>+140.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>284467308563</v>
+        <v>313709843048</v>
       </c>
       <c r="P2" t="n">
         <v>5660</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스팩주 특성상 단기 수익 기대. 신재생 에너지 합병 관련 언급 있으며, 2천원 종가 예상 및 타이밍 중요성 강조.</t>
+          <t>합병 대상 업종(신재생에너지)에 대한 언급과 스팩주의 일반적인 주가 패턴에 대한 의견 교환. 단기 수익 실현 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생 에너지', '단기 수익']</t>
+          <t>['스팩주', '합병', '수익']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14910</v>
+        <v>14990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.33%</t>
+          <t>+23.99%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -693,7 +693,7 @@
         <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>14910</v>
+        <v>15100</v>
       </c>
       <c r="M3" t="n">
         <v>12720</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>106797590820</v>
+        <v>133418021815</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>중동 긴장 고조 및 유가 급등에 따른 주가 상승 기대. 트럼프 발언 및 유가 전망 관련 분석.</t>
+          <t>이란발 지정학적 리스크로 인한 유가 급등에 따른 기대감 표현. 단기 매매 및 유가 변동성 주의 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가 급등', '중동 긴장', '트럼프']</t>
+          <t>['유가', '이란', '지정학적']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8470</v>
+        <v>8350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+14.15%</t>
+          <t>+12.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="H4" t="n">
         <v>1.17</v>
@@ -794,7 +794,7 @@
         <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>38687484830</v>
+        <v>41975027490</v>
       </c>
       <c r="P4" t="n">
         <v>21500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 폐암학회 참여 및 키투르다 관련 임상 결과 발표. 항암제 내성 극복 기대감으로 인한 주가 급등 전망.</t>
+          <t>항암제 내성 극복 및 임상 성공에 대한 강한 기대감 표현. 글로벌 제약사 참여 및 오가노이드 기술 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['폐암학회', '키투르다', '항암제 내성']</t>
+          <t>['항암제', '임상', '오가노이드']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>161700</v>
+        <v>158400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+5.34%</t>
+          <t>+3.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H5" t="n">
         <v>15.65</v>
@@ -886,7 +886,7 @@
         <v>15.25</v>
       </c>
       <c r="O5" t="n">
-        <v>149308564200</v>
+        <v>181131186300</v>
       </c>
       <c r="P5" t="n">
         <v>164700</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제마진 개선에 따른 긍정적 전망. 외인 대량 매수 이후 패턴 분석 및 주가 상승 기대.</t>
+          <t>고유가 상황 속 긍정적 전망, 정제마진 및 유가 상승에 따른 수익 기대. JP모건 매수 패턴 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', '외인 매수']</t>
+          <t>['유가', '정제마진', 'JP모건']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2125</v>
+        <v>2105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.34</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
         <v>0.85</v>
@@ -972,13 +972,13 @@
         <v>2395</v>
       </c>
       <c r="M6" t="n">
-        <v>2085</v>
+        <v>2075</v>
       </c>
       <c r="N6" t="n">
         <v>0.51</v>
       </c>
       <c r="O6" t="n">
-        <v>12340697343</v>
+        <v>13079081685</v>
       </c>
       <c r="P6" t="n">
         <v>2930</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>거래량 증가 및 주가 상승에 대한 기대감. 경영진 긍정 평가 및 매물 소화 관련 언급.</t>
+          <t>거래량 급증 및 경영진에 대한 긍정적 언급과 함께, 투자자들의 불안감 및 저항선에 대한 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['거래량', '주가 상승', '경영진']</t>
+          <t>['거래량', '경영진', '저항선']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1849000</v>
+        <v>1832000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="F7" t="n">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="G7" t="n">
-        <v>1657</v>
+        <v>1403</v>
       </c>
       <c r="H7" t="n">
         <v>50.67</v>
@@ -1064,13 +1064,13 @@
         <v>1890000</v>
       </c>
       <c r="M7" t="n">
-        <v>1848000</v>
+        <v>1832000</v>
       </c>
       <c r="N7" t="n">
         <v>50.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1075477771000</v>
+        <v>1311335510500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ADR 상승에 따른 본장 급등 기대감. 매물 부족 및 저점 매수 찬스 언급. 200 돌파 가능성 제기.</t>
+          <t>ADR 신고가 및 프리장 흐름을 기반으로 한 강한 상승 기대감 표현. 리밸런싱 물량 부담 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['ADR', '급등 기대', '저점 매수']</t>
+          <t>['ADR', '프리장', '상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>267000</v>
+        <v>265500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F8" t="n">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G8" t="n">
-        <v>2052</v>
+        <v>1790</v>
       </c>
       <c r="H8" t="n">
         <v>46.81</v>
@@ -1156,13 +1156,13 @@
         <v>270500</v>
       </c>
       <c r="M8" t="n">
-        <v>266500</v>
+        <v>265500</v>
       </c>
       <c r="N8" t="n">
         <v>46.85</v>
       </c>
       <c r="O8" t="n">
-        <v>532159491250</v>
+        <v>622498905500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>하이닉스 대비 삼성전자 주가 부진에 대한 언급 다수. 일부 투자자는 외국인 매도세 및 자사주 매입 관련 리스크 제기.</t>
+          <t>하이닉스와의 비교 속 부진한 주가 흐름, 자사주 매입 리스크 언급. 정치 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['하이닉스', '외국인 매도', '자사주']</t>
+          <t>['자사주', '하이닉스', '주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19020</v>
+        <v>18860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H9" t="n">
         <v>10.64</v>
@@ -1254,7 +1254,7 @@
         <v>10.85</v>
       </c>
       <c r="O9" t="n">
-        <v>29561633500</v>
+        <v>32811826595</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89500</v>
+        <v>88700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.40%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G10" t="n">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="H10" t="n">
         <v>23.65</v>
@@ -1346,7 +1346,7 @@
         <v>23.61</v>
       </c>
       <c r="O10" t="n">
-        <v>47170860100</v>
+        <v>54312506650</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14520</v>
+        <v>14410</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1.34</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="H11" t="n">
         <v>2.89</v>
@@ -1438,7 +1438,7 @@
         <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>45206750260</v>
+        <v>51488297895</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 부각되며 16000원 돌파 기대감이 형성되었으나, 외인 인기 순위 1위 등에도 불구하고 상승 추세는 불확실함. 시외 상승 후 급락 가능성도 제기됨.</t>
+          <t>미국 광통신 관련주로 언급되며, 16,000원 돌파 기대감과 함께 외인 인기가 높은 것으로 나타남. 다만, 일부 부정적 의견과 함께 급락 가능성도 제기됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AI 관련주', '시간외']</t>
+          <t>['광통신', 'AI', '시간외']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13740</v>
+        <v>14920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>-4.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="H12" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14320</v>
+        <v>15640</v>
       </c>
       <c r="K12" t="n">
-        <v>13800</v>
+        <v>15600</v>
       </c>
       <c r="L12" t="n">
-        <v>13900</v>
+        <v>15600</v>
       </c>
       <c r="M12" t="n">
-        <v>13260</v>
+        <v>14845</v>
       </c>
       <c r="N12" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>45246109425</v>
+        <v>10847373930</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-82000</v>
+        <v>-9000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>공매도 금지 지정 관련 언급. 일부 투자자는 주가 하락 예상 및 단타 매매 전략 제시. 그래핀 개발 관련 내용도 포함.</t>
+          <t>주가 하락세 지속 및 재료 약화에 대한 실망감 표현. 반도체 인재 양성 등 지역 개발 이슈 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도 금지', '주가 하락', '그래핀']</t>
+          <t>['주가', '재료', '반도체']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6510</v>
+        <v>13500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.10%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.03</v>
+        <v>0.45</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="H13" t="n">
-        <v>15.68</v>
+        <v>6.09</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6860</v>
+        <v>14320</v>
       </c>
       <c r="K13" t="n">
-        <v>6800</v>
+        <v>13800</v>
       </c>
       <c r="L13" t="n">
-        <v>6820</v>
+        <v>13900</v>
       </c>
       <c r="M13" t="n">
-        <v>6490</v>
+        <v>13260</v>
       </c>
       <c r="N13" t="n">
-        <v>16.71</v>
+        <v>5.64</v>
       </c>
       <c r="O13" t="n">
-        <v>4586562845</v>
+        <v>50989762540</v>
       </c>
       <c r="P13" t="n">
-        <v>13000</v>
+        <v>30200</v>
       </c>
       <c r="Q13" t="n">
-        <v>6030</v>
+        <v>3540</v>
       </c>
       <c r="R13" t="n">
-        <v>-20000</v>
+        <v>-82000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 주가 하락에 대한 우려. 로봇 및 반도체 관련 기대감에도 불구하고 주가 흐름 부진.</t>
+          <t>공매도 금지 조치에도 불구하고 하락세를 예상하며 단기 매도 의견 제시. 그래핀 개발 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인 매도', '로봇', '주가 하락']</t>
+          <t>['공매도', '하락', '그래핀']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12350</v>
+        <v>12260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.22%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.22</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H14" t="n">
         <v>0.14</v>
@@ -1714,7 +1714,7 @@
         <v>0.36</v>
       </c>
       <c r="O14" t="n">
-        <v>35283481460</v>
+        <v>37674448945</v>
       </c>
       <c r="P14" t="n">
         <v>20850</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>3500억 달러 규모의 대미 투자 관련 호재가 언급되었으나, 주가는 5% 이상 하락하며 투자자들의 불안감이 커지고 있음. 일부 투자자는 매도 후 다른 종목으로 이동함.</t>
+          <t>창사 이래 최대 호재 및 3500억 달러 규모 대미 투자 관련 언급이 있으나, 원전 하락세와 더불어 5% 이상 하락하며 투자자들의 혼란과 부정적인 심리가 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대미 투자', '원전', '악재']</t>
+          <t>['대미 투자', '원전', '호재']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1753,6 +1753,98 @@
       <c r="Z14" t="inlineStr">
         <is>
           <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6430</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-6.27%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E15" t="n">
+        <v>51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>131</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>6860</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6820</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6400</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5839987155</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6030</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>외국인 매도세와 주가 장난질에 대한 부정적 인식, 잡주 취급. 로봇/반도체 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['외국인', '주가', '로봇']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0220W0</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260910_09.xlsx
+++ b/data/trending_integrated_20260910_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4800</v>
+        <v>4990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+140.00%</t>
+          <t>+149.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>313709843048</v>
+        <v>377384884908</v>
       </c>
       <c r="P2" t="n">
         <v>5660</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 대상 업종(신재생에너지)에 대한 언급과 스팩주의 일반적인 주가 패턴에 대한 의견 교환. 단기 수익 실현 언급.</t>
+          <t>엔에이치스팩34호, 합병 대상 업종 신재생에너지 관련 기대감 있으나 스팩주 특성상 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '합병', '수익']</t>
+          <t>['스팩주', '신재생에너지', '하락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14990</v>
+        <v>14980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.99%</t>
+          <t>+23.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -693,7 +693,7 @@
         <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>15100</v>
+        <v>15120</v>
       </c>
       <c r="M3" t="n">
         <v>12720</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>133418021815</v>
+        <v>150781273085</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크로 인한 유가 급등에 따른 기대감 표현. 단기 매매 및 유가 변동성 주의 언급.</t>
+          <t>흥구석유, 중동 긴장 고조로 인한 유가 급등세 속 상승 기대감. 단기 차익 실현 매물 가능성도 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가', '이란', '지정학적']</t>
+          <t>['유가급등', '중동', '차익실현']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8350</v>
+        <v>3580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+12.53%</t>
+          <t>+15.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>675</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7420</v>
+        <v>3105</v>
       </c>
       <c r="K4" t="n">
-        <v>8000</v>
+        <v>3170</v>
       </c>
       <c r="L4" t="n">
-        <v>9100</v>
+        <v>3775</v>
       </c>
       <c r="M4" t="n">
-        <v>8000</v>
+        <v>3165</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>41975027490</v>
+        <v>14153552503</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>20800</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="R4" t="n">
-        <v>108000</v>
+        <v>24000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>항암제 내성 극복 및 임상 성공에 대한 강한 기대감 표현. 글로벌 제약사 참여 및 오가노이드 기술 언급.</t>
+          <t>20% 이상 상승하며 외인 수급 긍정적 신호, 단기 과열 및 주가 조작 의혹 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['항암제', '임상', '오가노이드']</t>
+          <t>['수급', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>158400</v>
+        <v>7930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+6.87%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>493</v>
+        <v>743</v>
       </c>
       <c r="H5" t="n">
-        <v>15.65</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>153500</v>
+        <v>7420</v>
       </c>
       <c r="K5" t="n">
-        <v>155500</v>
+        <v>8000</v>
       </c>
       <c r="L5" t="n">
-        <v>164700</v>
+        <v>9100</v>
       </c>
       <c r="M5" t="n">
-        <v>154500</v>
+        <v>7930</v>
       </c>
       <c r="N5" t="n">
-        <v>15.25</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>181131186300</v>
+        <v>45351366880</v>
       </c>
       <c r="P5" t="n">
-        <v>164700</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>87700</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>56000</v>
+        <v>108000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>고유가 상황 속 긍정적 전망, 정제마진 및 유가 상승에 따른 수익 기대. JP모건 매수 패턴 언급.</t>
+          <t>페니트리움바이오, 세계 최초 항암제 내성 극복 기술 개발 성공 및 글로벌 제약사 참여 기대감. 5연상 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', 'JP모건']</t>
+          <t>['항암제내성', '오가노이드', '5연상']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2105</v>
+        <v>4005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+5.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2085</v>
+        <v>3810</v>
       </c>
       <c r="K6" t="n">
-        <v>2255</v>
+        <v>3870</v>
       </c>
       <c r="L6" t="n">
-        <v>2395</v>
+        <v>4250</v>
       </c>
       <c r="M6" t="n">
-        <v>2075</v>
+        <v>3660</v>
       </c>
       <c r="N6" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="O6" t="n">
-        <v>13079081685</v>
+        <v>87185636585</v>
       </c>
       <c r="P6" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>63000</v>
+        <v>365000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>거래량 급증 및 경영진에 대한 긍정적 언급과 함께, 투자자들의 불안감 및 저항선에 대한 논의.</t>
+          <t>빛과전자, AI 데이터센터·6G 광통신 기술 개발 발표로 인한 기대감. 투경 회피 및 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['거래량', '경영진', '저항선']</t>
+          <t>['AI', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1832000</v>
+        <v>158100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+3.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>780</v>
+        <v>225</v>
       </c>
       <c r="F7" t="n">
-        <v>457</v>
+        <v>115</v>
       </c>
       <c r="G7" t="n">
-        <v>1403</v>
+        <v>575</v>
       </c>
       <c r="H7" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K7" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L7" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M7" t="n">
-        <v>1832000</v>
+        <v>154500</v>
       </c>
       <c r="N7" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1311335510500</v>
+        <v>196907001300</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q7" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R7" t="n">
-        <v>-48000</v>
+        <v>56000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ADR 신고가 및 프리장 흐름을 기반으로 한 강한 상승 기대감 표현. 리밸런싱 물량 부담 언급.</t>
+          <t>SK이노베이션, 유가 폭등 및 정제마진 고공행진으로 인한 실적 개선 기대감. 단기 상승 후 조정 가능성도 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['ADR', '프리장', '상승']</t>
+          <t>['유가폭등', '정제마진', '실적개선']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>265500</v>
+        <v>2120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>0.34</v>
       </c>
       <c r="E8" t="n">
-        <v>791</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>471</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>1790</v>
+        <v>104</v>
       </c>
       <c r="H8" t="n">
-        <v>46.81</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>269500</v>
+        <v>2085</v>
       </c>
       <c r="K8" t="n">
-        <v>269000</v>
+        <v>2255</v>
       </c>
       <c r="L8" t="n">
-        <v>270500</v>
+        <v>2395</v>
       </c>
       <c r="M8" t="n">
-        <v>265500</v>
+        <v>2075</v>
       </c>
       <c r="N8" t="n">
-        <v>46.85</v>
+        <v>0.51</v>
       </c>
       <c r="O8" t="n">
-        <v>622498905500</v>
+        <v>13535012145</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>2930</v>
       </c>
       <c r="Q8" t="n">
-        <v>71600</v>
+        <v>910</v>
       </c>
       <c r="R8" t="n">
-        <v>68000</v>
+        <v>63000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>하이닉스와의 비교 속 부진한 주가 흐름, 자사주 매입 리스크 언급. 정치 관련 언급 다수.</t>
+          <t>강동씨앤엘, 단기 급등 후 차익 실현 매물 출회 및 저항선 언급. 일부 부정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주', '하이닉스', '주가']</t>
+          <t>['차익실현', '저항선', '부정적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18860</v>
+        <v>1836000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.21</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>785</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>458</v>
       </c>
       <c r="G9" t="n">
-        <v>172</v>
+        <v>1384</v>
       </c>
       <c r="H9" t="n">
-        <v>10.64</v>
+        <v>50.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19450</v>
+        <v>1856000</v>
       </c>
       <c r="K9" t="n">
-        <v>18900</v>
+        <v>1879000</v>
       </c>
       <c r="L9" t="n">
-        <v>19220</v>
+        <v>1890000</v>
       </c>
       <c r="M9" t="n">
-        <v>18670</v>
+        <v>1829000</v>
       </c>
       <c r="N9" t="n">
-        <v>10.85</v>
+        <v>50.66</v>
       </c>
       <c r="O9" t="n">
-        <v>32811826595</v>
+        <v>1496230542000</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>293000</v>
       </c>
       <c r="R9" t="n">
-        <v>87000</v>
+        <v>-48000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 및 중동 정세 언급. 일부 투자자는 주가 하락 이유 분석 및 반등 기대.</t>
+          <t>SK하이닉스, ADR 상승에 따른 본장 급등 기대감 있으나 대규모 매도 물량 출회 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '중동', '주가 분석']</t>
+          <t>['ADR', '급등', '매도물량']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88700</v>
+        <v>265750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>784</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>467</v>
       </c>
       <c r="G10" t="n">
-        <v>622</v>
+        <v>1560</v>
       </c>
       <c r="H10" t="n">
-        <v>23.65</v>
+        <v>46.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>91700</v>
+        <v>269500</v>
       </c>
       <c r="K10" t="n">
-        <v>90000</v>
+        <v>269000</v>
       </c>
       <c r="L10" t="n">
-        <v>90700</v>
+        <v>270500</v>
       </c>
       <c r="M10" t="n">
-        <v>88400</v>
+        <v>265000</v>
       </c>
       <c r="N10" t="n">
-        <v>23.61</v>
+        <v>46.85</v>
       </c>
       <c r="O10" t="n">
-        <v>54312506650</v>
+        <v>737857933500</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>71600</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>68000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전 관련주로서 최고 호재가 부각되며 10만원 터치 기대감이 형성됨. 웨스팅하우스 지분 인수 가능성 및 '팀 코리아'의 미국 원전 건설 참여 소식이 긍정적 요인으로 작용하나, 외인 트릭 및 공매도에 대한 경계심도 존재함.</t>
+          <t>삼성전자, 자사주 매입 리스크와 주주환원 요구 제기. 일부 투자자 매도 의견.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', '팀 코리아']</t>
+          <t>['자사주매입', '주주환원', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14410</v>
+        <v>18960</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.34</v>
+        <v>-0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="H11" t="n">
-        <v>2.89</v>
+        <v>10.64</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14960</v>
+        <v>19450</v>
       </c>
       <c r="K11" t="n">
-        <v>15040</v>
+        <v>18900</v>
       </c>
       <c r="L11" t="n">
-        <v>15040</v>
+        <v>19220</v>
       </c>
       <c r="M11" t="n">
-        <v>14190</v>
+        <v>18670</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>10.85</v>
       </c>
       <c r="O11" t="n">
-        <v>51488297895</v>
+        <v>36005098945</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>1263</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-191000</v>
+        <v>87000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 언급되며, 16,000원 돌파 기대감과 함께 외인 인기가 높은 것으로 나타남. 다만, 일부 부정적 의견과 함께 급락 가능성도 제기됨.</t>
+          <t>대우건설, 미국 투자 및 원전 관련 긍정적 기대감 속 급등 가능성 언급. 일부는 하락 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '시간외']</t>
+          <t>['미국투자', '원전', '급등']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14920</v>
+        <v>89000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.60%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="G12" t="n">
-        <v>143</v>
+        <v>601</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15640</v>
+        <v>91700</v>
       </c>
       <c r="K12" t="n">
-        <v>15600</v>
+        <v>90000</v>
       </c>
       <c r="L12" t="n">
-        <v>15600</v>
+        <v>90700</v>
       </c>
       <c r="M12" t="n">
-        <v>14845</v>
+        <v>88400</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="O12" t="n">
-        <v>10847373930</v>
+        <v>62734295950</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-9000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 재료 약화에 대한 실망감 표현. 반도체 인재 양성 등 지역 개발 이슈 언급.</t>
+          <t>원전 사업 수주 기대감 및 웨스팅하우스 인수전 참여 가능성, 10만원 터치 및 전약후강 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가', '재료', '반도체']</t>
+          <t>['원전', '수주', '인수전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13500</v>
+        <v>14440</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.73%</t>
+          <t>-3.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.45</v>
+        <v>1.34</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>202</v>
+        <v>300</v>
       </c>
       <c r="H13" t="n">
-        <v>6.09</v>
+        <v>2.89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14320</v>
+        <v>14960</v>
       </c>
       <c r="K13" t="n">
-        <v>13800</v>
+        <v>15040</v>
       </c>
       <c r="L13" t="n">
-        <v>13900</v>
+        <v>15040</v>
       </c>
       <c r="M13" t="n">
-        <v>13260</v>
+        <v>14190</v>
       </c>
       <c r="N13" t="n">
-        <v>5.64</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>50989762540</v>
+        <v>55550569390</v>
       </c>
       <c r="P13" t="n">
-        <v>30200</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3540</v>
+        <v>1263</v>
       </c>
       <c r="R13" t="n">
-        <v>-82000</v>
+        <v>-191000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 금지 조치에도 불구하고 하락세를 예상하며 단기 매도 의견 제시. 그래핀 개발 관련 언급.</t>
+          <t>미국 광통신 시장 강세 및 AI 관련주 부각, 외인 매수세 유입 및 16000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '하락', '그래핀']</t>
+          <t>['광통신', 'AI', '외인매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12260</v>
+        <v>28950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-4.46%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.22</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="H14" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13030</v>
+        <v>30300</v>
       </c>
       <c r="K14" t="n">
-        <v>13160</v>
+        <v>30800</v>
       </c>
       <c r="L14" t="n">
-        <v>13240</v>
+        <v>31500</v>
       </c>
       <c r="M14" t="n">
-        <v>12150</v>
+        <v>28150</v>
       </c>
       <c r="N14" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="O14" t="n">
-        <v>37674448945</v>
+        <v>59243029750</v>
       </c>
       <c r="P14" t="n">
-        <v>20850</v>
+        <v>39350</v>
       </c>
       <c r="Q14" t="n">
-        <v>4020</v>
+        <v>8200</v>
       </c>
       <c r="R14" t="n">
-        <v>-6000</v>
+        <v>25000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 및 3500억 달러 규모 대미 투자 관련 언급이 있으나, 원전 하락세와 더불어 5% 이상 하락하며 투자자들의 혼란과 부정적인 심리가 나타남.</t>
+          <t>하락 추세 지속, 3만원 지지선 이탈 및 폭포수 같은 급락 우려, 매수세 실종.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대미 투자', '원전', '호재']</t>
+          <t>['하락', '지지선', '매수세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6430</v>
+        <v>14910</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-6.27%</t>
+          <t>-4.67%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="H15" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,58 +1791,334 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K15" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L15" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M15" t="n">
-        <v>6400</v>
+        <v>14770</v>
       </c>
       <c r="N15" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5839987155</v>
+        <v>12870840320</v>
       </c>
       <c r="P15" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-20000</v>
+        <v>-9000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 매도세와 주가 장난질에 대한 부정적 인식, 잡주 취급. 로봇/반도체 관련 언급.</t>
+          <t>금호건설, 일부 호재 언급 있으나 전반적으로 부정적 전망과 투매 의견 지배적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['호재', '부정적전망', '투매']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13650</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-4.68%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E16" t="n">
+        <v>62</v>
+      </c>
+      <c r="F16" t="n">
+        <v>46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>222</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>14320</v>
+      </c>
+      <c r="K16" t="n">
+        <v>13800</v>
+      </c>
+      <c r="L16" t="n">
+        <v>13900</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="O16" t="n">
+        <v>53633826020</v>
+      </c>
+      <c r="P16" t="n">
+        <v>30200</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3540</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-82000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>그래핀 개발 호재에도 불구하고 하락세 전망, 공매도 금지 영향 언급.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
         <v>0.1</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['그래핀', '공매도', '하락']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>032820</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12260</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-5.91%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>43</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>13030</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13160</v>
+      </c>
+      <c r="L17" t="n">
+        <v>13240</v>
+      </c>
+      <c r="M17" t="n">
+        <v>12150</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O17" t="n">
+        <v>40183932945</v>
+      </c>
+      <c r="P17" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>대규모 대미 투자 호재에도 불구하고 하락세, 개인 투자자들의 차익 실현 및 주포 움직임 주시.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['대미투자', '하락', '주포']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>한화머시너리앤서비스홀딩스</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6450</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-5.98%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57</v>
+      </c>
+      <c r="F18" t="n">
+        <v>39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>140</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6860</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6820</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6400</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6228637870</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6030</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>외국인 매도세와 주가 장난질에 대한 부정적 인식, 잡주 취급. 로봇/반도체 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>['외국인', '주가', '로봇']</t>
         </is>
       </c>
-      <c r="X15" t="n">
+      <c r="X18" t="n">
         <v>11</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>0220W0</t>
         </is>
